--- a/output/graficos_dimensiones/comunal_o_ocup_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:52</t>
+    <t xml:space="preserve">2026-09-09 22:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:40</t>
+    <t xml:space="preserve">2026-09-18 10:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:02</t>
+    <t xml:space="preserve">2026-09-23 12:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:08</t>
+    <t xml:space="preserve">2026-10-02 13:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2020_nuble.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Ñiquén</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">San Fabián</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:43</t>
+    <t xml:space="preserve">2026-10-04 08:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:25</t>
+    <t xml:space="preserve">2026-10-05 08:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
